--- a/CORE/Localization/MTextLocalization.xlsx
+++ b/CORE/Localization/MTextLocalization.xlsx
@@ -78,6 +78,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>你好</t>
     </r>
     <r>
@@ -105,6 +110,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>{color=#ffcc00}</t>
     </r>
     <r>
@@ -763,7 +773,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -772,9 +782,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1415,21 +1422,21 @@
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="2" t="s">
         <v>18</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="4"/>
+      <c r="C5" s="2"/>
       <c r="D5" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4" t="s">
+      <c r="E5" s="2"/>
+      <c r="F5" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="2" t="s">
         <v>20</v>
       </c>
     </row>
